--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -101,10 +101,10 @@
     <t>Consignee City Name</t>
   </si>
   <si>
-    <t>Delivey Type ID</t>
-  </si>
-  <si>
     <t>Charges Mode ID</t>
+  </si>
+  <si>
+    <t>Delivery Type ID</t>
   </si>
 </sst>
 </file>
@@ -495,10 +495,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -462,29 +462,30 @@
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
@@ -498,76 +499,76 @@
         <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Mode of Payment ID</t>
-  </si>
-  <si>
-    <t>Pickup Date (YYYY-MM-DD)</t>
   </si>
   <si>
     <t>Item Product Type ID</t>
@@ -110,7 +107,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -457,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -478,17 +475,16 @@
     <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -496,13 +492,13 @@
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -511,10 +507,10 @@
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -523,7 +519,7 @@
         <v>3</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -532,13 +528,13 @@
         <v>5</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>7</v>
@@ -547,28 +543,25 @@
         <v>8</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7D84E1-578C-41A3-B1CB-AACBC35DB134}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -102,12 +103,15 @@
   </si>
   <si>
     <t>Delivery Type ID</t>
+  </si>
+  <si>
+    <t>Pieces</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -453,8 +457,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -481,10 +485,11 @@
     <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -562,6 +567,9 @@
       </c>
       <c r="Z1" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7D84E1-578C-41A3-B1CB-AACBC35DB134}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F9E5CD-1A97-47EA-A684-98967CC0B68F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Pieces</t>
+  </si>
+  <si>
+    <t>Self Collection</t>
   </si>
 </sst>
 </file>
@@ -458,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -470,26 +473,27 @@
     <col min="7" max="7" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="21.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -521,54 +525,57 @@
         <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F9E5CD-1A97-47EA-A684-98967CC0B68F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0911FA0-20E4-4261-AAA4-AB4B8EC42E17}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Self Collection</t>
+  </si>
+  <si>
+    <t>Order Date  (YYYY-MM-DD)</t>
   </si>
 </sst>
 </file>
@@ -461,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -475,25 +478,26 @@
     <col min="10" max="10" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.33203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -531,51 +535,54 @@
         <v>3</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0911FA0-20E4-4261-AAA4-AB4B8EC42E17}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1738DE4D-7347-4809-B746-587258C9CCFF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -112,6 +112,21 @@
   </si>
   <si>
     <t>Order Date  (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 1</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 3</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 4</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 5</t>
   </si>
 </sst>
 </file>
@@ -464,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -495,9 +510,10 @@
     <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="8.88671875" style="1"/>
+    <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -584,6 +600,21 @@
       </c>
       <c r="AC1" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1738DE4D-7347-4809-B746-587258C9CCFF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF77651-3750-490B-AFD4-58AA323218F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
+  </si>
+  <si>
+    <t>Open Shipment</t>
   </si>
 </sst>
 </file>
@@ -479,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -513,7 +516,7 @@
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -615,6 +618,9 @@
       </c>
       <c r="AH1" t="s">
         <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF77651-3750-490B-AFD4-58AA323218F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26210835-4133-4C92-999C-3D2153C57ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Return Address ID</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -516,7 +519,7 @@
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -621,6 +624,9 @@
       </c>
       <c r="AI1" t="s">
         <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26210835-4133-4C92-999C-3D2153C57ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC86DFD-74F0-459C-BC49-CEA38C613B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Open Shipment</t>
-  </si>
-  <si>
-    <t>Return Address ID</t>
   </si>
 </sst>
 </file>
@@ -485,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -519,7 +516,7 @@
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -624,9 +621,6 @@
       </c>
       <c r="AI1" t="s">
         <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC86DFD-74F0-459C-BC49-CEA38C613B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF77651-3750-490B-AFD4-58AA323218F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF77651-3750-490B-AFD4-58AA323218F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC63B728-3835-4ED5-B9F5-AC514C75328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Trax Center/Franchise Type</t>
+  </si>
+  <si>
+    <t>Trax Center/Franchise ID</t>
   </si>
 </sst>
 </file>
@@ -482,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -514,9 +520,12 @@
     <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="8.88671875" style="1"/>
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -621,6 +630,12 @@
       </c>
       <c r="AI1" t="s">
         <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC63B728-3835-4ED5-B9F5-AC514C75328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8354B841-B35C-43F6-BF41-2864D4B90922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2088" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -130,12 +130,6 @@
   </si>
   <si>
     <t>Open Shipment</t>
-  </si>
-  <si>
-    <t>Trax Center/Franchise Type</t>
-  </si>
-  <si>
-    <t>Trax Center/Franchise ID</t>
   </si>
 </sst>
 </file>
@@ -488,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -525,7 +519,7 @@
     <col min="37" max="37" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -630,12 +624,6 @@
       </c>
       <c r="AI1" t="s">
         <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8354B841-B35C-43F6-BF41-2864D4B90922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF77651-3750-490B-AFD4-58AA323218F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2088" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -514,9 +514,6 @@
     <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="8.88671875" style="1"/>
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF77651-3750-490B-AFD4-58AA323218F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BDAA75-3337-4D86-BFA0-9EBA432E7140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Parcel Value</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -516,7 +519,7 @@
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -621,6 +624,9 @@
       </c>
       <c r="AI1" t="s">
         <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BDAA75-3337-4D86-BFA0-9EBA432E7140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0D79DD-35EA-4B7C-9DD9-A57F3B312666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -517,6 +517,7 @@
     <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="8.88671875" style="1"/>
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.3">
@@ -625,7 +626,7 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0D79DD-35EA-4B7C-9DD9-A57F3B312666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -133,12 +132,18 @@
   </si>
   <si>
     <t>Parcel Value</t>
+  </si>
+  <si>
+    <t>Consignee Address Latitude</t>
+  </si>
+  <si>
+    <t>Consignee Address Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -484,8 +489,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -497,30 +502,30 @@
     <col min="7" max="7" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.33203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.88671875" style="1"/>
-    <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.88671875" style="1"/>
+    <col min="11" max="13" width="21.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.21875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.88671875" style="1"/>
+    <col min="32" max="36" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -552,81 +557,87 @@
         <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>35</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>Consignee Address Longitude</t>
+  </si>
+  <si>
+    <t>Retail Pickup Store ID</t>
+  </si>
+  <si>
+    <t>Retail Deliver Store ID</t>
   </si>
 </sst>
 </file>
@@ -490,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -525,7 +531,7 @@
     <col min="38" max="38" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -639,6 +645,12 @@
       </c>
       <c r="AL1" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
